--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.69.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.69.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -819,7 +819,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.69.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.69.xlsx
@@ -422,20 +422,20 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
     <col width="60" customWidth="1" min="9" max="9"/>
-    <col width="27" customWidth="1" min="10" max="10"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
-    <col width="40" customWidth="1" min="14" max="14"/>
-    <col width="35" customWidth="1" min="15" max="15"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="14" max="14"/>
+    <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
-    <col width="30" customWidth="1" min="17" max="17"/>
+    <col width="60" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
     <col width="60" customWidth="1" min="19" max="19"/>
     <col width="30" customWidth="1" min="20" max="20"/>
@@ -599,22 +599,38 @@
           <t>L25: suspicious token(s): aLVII (odd internal casing) :: aLVII. to be examined.</t>
         </is>
       </c>
-      <c r="J2" s="1" t="inlineStr"/>
+      <c r="J2" s="1" t="inlineStr">
+        <is>
+          <t>L73: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
+        </is>
+      </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L7: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: LVII. he has been examined, under the following order :â€”</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]62</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]62</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L16: isolated marker/symbol line :: 62</t>
         </is>
       </c>
-      <c r="O2" s="1" t="inlineStr"/>
+      <c r="O2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]62</t>
+        </is>
+      </c>
       <c r="P2" s="1" t="inlineStr"/>
-      <c r="Q2" s="1" t="inlineStr"/>
+      <c r="Q2" s="1" t="inlineStr">
+        <is>
+          <t>L10: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: hyphen/bullet debris :: vided may be further examined, on his own behalf, in re-•</t>
+        </is>
+      </c>
       <c r="R2" s="1" t="inlineStr"/>
       <c r="S2" s="1" t="inlineStr">
         <is>
@@ -645,7 +661,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>89</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -661,14 +677,14 @@
       <c r="J3" s="1" t="inlineStr"/>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L10: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: vided may be further examined, on his own behalf, in re-â€¢</t>
+          <t>L10: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: hyphen/bullet debris :: vided may be further examined, on his own behalf, in re-•</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
       <c r="N3" s="1" t="inlineStr">
         <is>
-          <t>L113: isolated marker/symbol line :: 2</t>
+          <t>L73: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
         </is>
       </c>
       <c r="O3" s="1" t="inlineStr"/>
@@ -712,12 +728,16 @@
       <c r="J4" s="1" t="inlineStr"/>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L42: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: .â€˜ lication, or otherwise, as to the Court may seem just.</t>
+          <t>L79: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: the ends €</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
-      <c r="N4" s="1" t="inlineStr"/>
+      <c r="N4" s="1" t="inlineStr">
+        <is>
+          <t>L113: isolated marker/symbol line :: 2</t>
+        </is>
+      </c>
       <c r="O4" s="1" t="inlineStr"/>
       <c r="P4" s="1" t="inlineStr"/>
       <c r="Q4" s="1" t="inlineStr"/>
@@ -738,12 +758,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -753,11 +773,7 @@
       <c r="H5" s="1" t="inlineStr"/>
       <c r="I5" s="1" t="inlineStr"/>
       <c r="J5" s="1" t="inlineStr"/>
-      <c r="K5" s="1" t="inlineStr">
-        <is>
-          <t>L60: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Order :â€”</t>
-        </is>
-      </c>
+      <c r="K5" s="1" t="inlineStr"/>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr"/>
@@ -796,11 +812,7 @@
       <c r="H6" s="1" t="inlineStr"/>
       <c r="I6" s="1" t="inlineStr"/>
       <c r="J6" s="1" t="inlineStr"/>
-      <c r="K6" s="1" t="inlineStr">
-        <is>
-          <t>L79: stray/suspicious non-ASCII glyph(s): U+00AC NOT SIGN :: the ends â‚¬</t>
-        </is>
-      </c>
+      <c r="K6" s="1" t="inlineStr"/>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr"/>
@@ -941,12 +953,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -985,7 +997,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1019,12 +1031,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1063,7 +1075,7 @@
       </c>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D13" s="1" t="inlineStr"/>
